--- a/public/交易明细填写模板.xlsx
+++ b/public/交易明细填写模板.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="22420"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="sheet" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>年</t>
   </si>
@@ -48,6 +48,12 @@
   </si>
   <si>
     <t>业务类型</t>
+  </si>
+  <si>
+    <t>归属项目</t>
+  </si>
+  <si>
+    <t>费用类型</t>
   </si>
   <si>
     <t>备注</t>
@@ -1252,14 +1258,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="1"/>
+  <dimension ref="A1:L2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
-    <col min="4" max="7" width="15" customWidth="1"/>
-    <col min="9" max="10" width="15" customWidth="1"/>
+    <col min="4" max="9" width="15" customWidth="1"/>
+    <col min="11" max="12" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21" spans="1:10">
+    <row r="1" ht="18.75" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1290,8 +1296,14 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" ht="15" spans="1:12">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -1302,6 +1314,8 @@
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/public/交易明细填写模板.xlsx
+++ b/public/交易明细填写模板.xlsx
@@ -50,10 +50,10 @@
     <t>业务类型</t>
   </si>
   <si>
-    <t>归属项目</t>
+    <t>归属项目名称</t>
   </si>
   <si>
-    <t>费用类型</t>
+    <t>费用类型名称</t>
   </si>
   <si>
     <t>备注</t>
@@ -75,7 +75,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -92,6 +92,11 @@
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -572,152 +577,152 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -725,6 +730,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1258,14 +1264,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
+  <dimension ref="A1:L4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3"/>
   <cols>
     <col min="4" max="9" width="15" customWidth="1"/>
     <col min="11" max="12" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18.75" spans="1:12">
+    <row r="1" ht="37.5" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1311,11 +1317,35 @@
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
+    </row>
+    <row r="3" ht="15" spans="1:12">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="K3" s="2"/>
+    </row>
+    <row r="4" ht="15" spans="1:12">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="K4" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
